--- a/db_storage/kibana.xlsx
+++ b/db_storage/kibana.xlsx
@@ -437,7 +437,7 @@
         <v>data_views</v>
       </c>
       <c r="B2" t="str">
-        <v>id,uuid,name,created_at,updated_at</v>
+        <v>id,uuid,name,default_fields,pop_fields,created_at,updated_at</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -478,9 +478,15 @@
         <v>name</v>
       </c>
       <c r="D1" t="str">
+        <v>default_fields</v>
+      </c>
+      <c r="E1" t="str">
+        <v>pop_fields</v>
+      </c>
+      <c r="F1" t="str">
         <v>created_at</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>updated_at</v>
       </c>
     </row>
@@ -489,16 +495,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>filebeat-casino-*</v>
+        <v>filebeat-*</v>
       </c>
       <c r="C2" t="str">
-        <v>filebeat-casino-*</v>
+        <v>filebeat-*</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-16T09:04:26.455Z</v>
+        <v>@timestamp,message</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-05-16T09:04:26.455Z</v>
+        <v>message, contextMap.uuid, contextMap.userId, contextMap.ppenv, loggerName, contextMap.gameId, host.name, contextMap.apiType, contextMap.tableId, threadId</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-05-20T20:39:46.215Z</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-05-20T20:42:49.179Z</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +518,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>filebeat-live-*</v>
+        <v>filebeat-casino-*</v>
       </c>
       <c r="C3" t="str">
-        <v>filebeat-live-*</v>
+        <v>filebeat-casino-*</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-16T09:04:45.674Z</v>
+        <v>@timestamp,message</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-05-16T09:04:45.674Z</v>
+        <v>message, contextMap.uuid, contextMap.userId, contextMap.ppenv, loggerName, contextMap.gameId, host.name, contextMap.apiType, contextMap.tableId, threadId</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-05-20T20:40:30.285Z</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-05-20T20:42:54.929Z</v>
       </c>
     </row>
     <row r="4">
@@ -523,16 +541,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>filebeat-slots</v>
+        <v>filebeat-live-*</v>
       </c>
       <c r="C4" t="str">
-        <v>filebeat-slots</v>
+        <v>filebeat-live-*</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-16T09:05:08.459Z</v>
+        <v>@timestamp,message</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-05-16T09:05:08.459Z</v>
+        <v>message, contextMap.uuid, contextMap.userId, contextMap.ppenv, loggerName, contextMap.gameId, host.name, contextMap.apiType, contextMap.tableId, threadId</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-05-20T20:40:54.268Z</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-05-20T20:43:01.214Z</v>
       </c>
     </row>
     <row r="5">
@@ -540,21 +564,50 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
+        <v>filebeat-slots-*</v>
+      </c>
+      <c r="C5" t="str">
+        <v>filebeat-slots-*</v>
+      </c>
+      <c r="D5" t="str">
+        <v>@timestamp,app.requestLog.log,app.responseLog.log,app.serviceMethod,app.url</v>
+      </c>
+      <c r="E5" t="str">
+        <v>@timestamp,message</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-05-20T20:41:28.471Z</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-05-20T20:54:03.257Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
         <v>filebeat-dealermodule-*</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
         <v>filebeat-dealermodule-*</v>
       </c>
-      <c r="D5" t="str">
-        <v>2026-05-16T09:05:29.795Z</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-05-16T09:05:29.795Z</v>
+      <c r="D6" t="str">
+        <v>@timestamp,message</v>
+      </c>
+      <c r="E6" t="str">
+        <v>@timestamp,message</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-05-20T20:42:22.935Z</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-05-20T20:43:12.073Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/db_storage/kibana.xlsx
+++ b/db_storage/kibana.xlsx
@@ -8,6 +8,7 @@
     <sheet name="data_views" sheetId="3" r:id="rId3"/>
     <sheet name="search_auto_compelete" sheetId="4" r:id="rId4"/>
     <sheet name="queries" sheetId="5" r:id="rId5"/>
+    <sheet name="stored_queries" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -422,7 +423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -456,9 +457,17 @@
         <v>id,name,game,filters,query,created_at,updated_at</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>stored_queries</v>
+      </c>
+      <c r="B5" t="str">
+        <v>id,title,query_string,filters,default_columns,index,description,created_at,updated_at</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1000,4 +1009,131 @@
     <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>query_string</v>
+      </c>
+      <c r="D1" t="str">
+        <v>filters</v>
+      </c>
+      <c r="E1" t="str">
+        <v>default_columns</v>
+      </c>
+      <c r="F1" t="str">
+        <v>index</v>
+      </c>
+      <c r="G1" t="str">
+        <v>description</v>
+      </c>
+      <c r="H1" t="str">
+        <v>created_at</v>
+      </c>
+      <c r="I1" t="str">
+        <v>updated_at</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Snap Monitoring</v>
+      </c>
+      <c r="C2" t="str">
+        <v>("callSnapServer " or "taking snap" or "an FFMPEG")</v>
+      </c>
+      <c r="D2" t="str">
+        <v>[{"id":"f_1781406984462","field":"host.name","type":"phrases","negate":false,"value":"{host.names}"}]</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>f777a02e-2716-4c3a-bb3c-a4be37741231</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Snap Monitoring with HOST NAME</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-06-14T03:16:53.157Z</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-06-14T10:09:58.082Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Slots Log</v>
+      </c>
+      <c r="C3" t="str">
+        <v>{round_id}</v>
+      </c>
+      <c r="D3" t="str">
+        <v>[{"id":"f_1781433305050","field":"app.serviceMethod","type":"exists","negate":false,"value":"exists"}]</v>
+      </c>
+      <c r="E3" t="str">
+        <v>app.requestLog.log, app.responseLog.log, app.serviceMethod, app.url</v>
+      </c>
+      <c r="F3" t="str">
+        <v>bd4b9c51-064f-45c5-81c2-49862139894d</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-06-14T10:32:21.232Z</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-06-14T17:36:23.128Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Baccarat</v>
+      </c>
+      <c r="C4" t="str">
+        <v>({round_id} OR ({game_id} AND {user_id})) OR ({game_id} AND (betsopen OR betsClose)) OR ({game_id} AND card)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>[]</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>8ddfb450-4bb6-11e9-9f5b-7759dded6c19</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Baccarat game logs</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-06-14T15:55:51.680Z</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-06-14T18:04:56.338Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+  </ignoredErrors>
+</worksheet>
 </file>